--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487722_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487722_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3658</v>
+        <v>2.9998</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5253</v>
+        <v>4.1865</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1595</v>
+        <v>-1.1867</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1579</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0078</v>
+        <v>-1.3739</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5624</v>
+        <v>-0.9012</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4454</v>
+        <v>-0.4727</v>
       </c>
       <c r="V2" t="n">
         <v>2.7853</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7466</v>
+        <v>1.3918</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0782</v>
+        <v>1.7779</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3317</v>
+        <v>-0.3862</v>
       </c>
       <c r="G3" t="n">
         <v>1.0868</v>
@@ -688,13 +688,13 @@
         <v>0.5821</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0733</v>
+        <v>-0.4281</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1951</v>
+        <v>-0.1052</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2685</v>
+        <v>-0.323</v>
       </c>
       <c r="V3" t="n">
         <v>0.1511</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2572</v>
+        <v>0.1746</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2822</v>
+        <v>1.3934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0251</v>
+        <v>-1.2188</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9308</v>
+        <v>0.4961</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5248</v>
+        <v>1.0183</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.406</v>
+        <v>-0.5222</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6467000000000001</v>
+        <v>2.1103</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.3853</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.284</v>
+        <v>-1.6142</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1219</v>
+        <v>0.2933</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.406</v>
+        <v>-1.9075</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2855</v>
+        <v>-1.0248</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3645</v>
+        <v>-0.717</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.079</v>
+        <v>-0.3078</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.4609</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.4609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3226</v>
+        <v>-0.3288</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0325</v>
+        <v>1.2235</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.355</v>
+        <v>-1.5523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4961</v>
+        <v>1.174</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0183</v>
+        <v>1.7079</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5222</v>
+        <v>-0.5339</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1103</v>
+        <v>2.0257</v>
       </c>
       <c r="K5" t="n">
-        <v>0.725</v>
+        <v>1.3306</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3853</v>
+        <v>0.6952</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6142</v>
+        <v>-0.8517</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2933</v>
+        <v>0.3773</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9075</v>
+        <v>-1.229</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.522</v>
+        <v>-0.7882</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0779</v>
+        <v>-0.6082</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4441</v>
+        <v>-0.18</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4609</v>
+        <v>-1.6848</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4609</v>
+        <v>-1.6848</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7776</v>
+        <v>-0.5758</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2604</v>
+        <v>-0.6826</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5172</v>
+        <v>0.1068</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5261</v>
+        <v>-0.9308</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0189</v>
+        <v>-0.5248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.545</v>
+        <v>-0.406</v>
       </c>
       <c r="J6" t="n">
-        <v>0.103</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.103</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.629</v>
+        <v>-0.284</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.1219</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.545</v>
+        <v>-0.406</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1337</v>
+        <v>-0.0331</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3634</v>
+        <v>-0.0359</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2297</v>
+        <v>0.0028</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8804</v>
+        <v>-0.741</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8627</v>
+        <v>-0.0602</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7431</v>
+        <v>-0.6808</v>
       </c>
       <c r="G7" t="n">
-        <v>1.174</v>
+        <v>-0.5261</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7079</v>
+        <v>0.0189</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5339</v>
+        <v>-0.545</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0257</v>
+        <v>0.103</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3306</v>
+        <v>0.103</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6952</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8517</v>
+        <v>-0.629</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3773</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.229</v>
+        <v>-0.545</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3398</v>
+        <v>-0.097</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9691</v>
+        <v>-0.1632</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3708</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6848</v>
+        <v>-0.894</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6848</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2936</v>
+        <v>-1.5394</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1005</v>
+        <v>-0.4008</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1931</v>
+        <v>-1.1386</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3854</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3156</v>
+        <v>0.0698</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5462</v>
+        <v>0.2459</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2306</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2239</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8827</v>
+        <v>-2.8572</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6015</v>
+        <v>-2.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2812</v>
+        <v>-0.8272</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9604</v>
+        <v>-2.1899</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1328</v>
+        <v>-0.3625</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0933</v>
+        <v>-1.8274</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0657</v>
+        <v>-0.5641</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9845</v>
+        <v>-0.5108</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0262</v>
+        <v>-1.6258</v>
       </c>
       <c r="N9" t="n">
         <v>0.1483</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1744</v>
+        <v>-1.774</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3777</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1552</v>
+        <v>-0.4958</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2226</v>
+        <v>-0.3656</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9418</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>G. ARTILES ROMERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2576</v>
+        <v>-2.9798</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4304</v>
+        <v>-1.0096</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8272</v>
+        <v>-1.9702</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1899</v>
+        <v>-0.3016</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3625</v>
+        <v>0.6377</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8274</v>
+        <v>-0.9393</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5641</v>
+        <v>0.7066</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5108</v>
+        <v>0.6838</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0533</v>
+        <v>0.0228</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6258</v>
+        <v>-1.0083</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1483</v>
+        <v>-0.0462</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.774</v>
+        <v>-0.9621</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="R10" t="n">
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2618</v>
+        <v>-0.7857</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8962</v>
+        <v>-0.4475</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3656</v>
+        <v>-0.3381</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. ARTILES ROMERO</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.353</v>
+        <v>-3.3889</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.41</v>
+        <v>-2.0518</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.943</v>
+        <v>-1.3371</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3016</v>
+        <v>-2.6394</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6377</v>
+        <v>0.0989</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9393</v>
+        <v>-2.7383</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7066</v>
+        <v>-1.0196</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6838</v>
+        <v>-0.4614</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0228</v>
+        <v>-0.5583</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0083</v>
+        <v>-1.6198</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0462</v>
+        <v>0.5602</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9621</v>
+        <v>-2.18</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1588</v>
+        <v>-1.0826</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8479</v>
+        <v>-0.8381</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3109</v>
+        <v>-0.2445</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0478</v>
+        <v>-1.025</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.788</v>
+        <v>-1.025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6407</v>
+        <v>-3.4054</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4127</v>
+        <v>-2.0425</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.228</v>
+        <v>-1.363</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6394</v>
+        <v>-0.9604</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0989</v>
+        <v>1.1328</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7383</v>
+        <v>-2.0933</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0196</v>
+        <v>1.0657</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4614</v>
+        <v>0.9845</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5583</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6198</v>
+        <v>-2.0262</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5602</v>
+        <v>0.1483</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.18</v>
+        <v>-2.1744</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3582</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3344</v>
+        <v>-0.145</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.199</v>
+        <v>-0.2858</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1354</v>
+        <v>0.1408</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.025</v>
+        <v>-0.9418</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.025</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.553</v>
+        <v>-11.2501</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001000000000000334</v>
+        <v>0.3037999999999994</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.5539</v>
+        <v>-11.5541</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.3346</v>
+        <v>-5.334600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1194</v>
+        <v>4.119400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-9.4541</v>
@@ -1444,7 +1444,7 @@
         <v>7.0528</v>
       </c>
       <c r="K13" t="n">
-        <v>1.491299999999999</v>
+        <v>1.4913</v>
       </c>
       <c r="L13" t="n">
         <v>5.5615</v>
@@ -1468,10 +1468,10 @@
         <v>11.642</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.8528</v>
+        <v>-6.55</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6549</v>
+        <v>-4.351999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>-2.198</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.7279</v>
+        <v>9.8436</v>
       </c>
       <c r="E14" t="n">
-        <v>7.8394</v>
+        <v>8.0396</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8885</v>
+        <v>1.8039</v>
       </c>
       <c r="G14" t="n">
         <v>6.9075</v>
@@ -1546,13 +1546,13 @@
         <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8966</v>
+        <v>1.0122</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0348</v>
+        <v>0.1654</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9314</v>
+        <v>0.8468</v>
       </c>
       <c r="V14" t="n">
         <v>2.1179</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0626</v>
+        <v>5.3145</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7621</v>
+        <v>3.9623</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3004</v>
+        <v>1.3521</v>
       </c>
       <c r="G15" t="n">
         <v>3.668</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6364</v>
+        <v>0.8883</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2165</v>
+        <v>-0.0163</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8529</v>
+        <v>0.9046</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0893</v>
+        <v>3.6866</v>
       </c>
       <c r="E16" t="n">
-        <v>3.892</v>
+        <v>4.1923</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8027</v>
+        <v>-0.5057</v>
       </c>
       <c r="G16" t="n">
         <v>1.0038</v>
@@ -1702,13 +1702,13 @@
         <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.6827</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0954</v>
+        <v>0.2049</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1808</v>
+        <v>0.4778</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6757</v>
+        <v>1.3114</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8345</v>
+        <v>2.334</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1588</v>
+        <v>-1.0226</v>
       </c>
       <c r="G17" t="n">
         <v>1.402</v>
@@ -1780,13 +1780,13 @@
         <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0498</v>
+        <v>0.6856</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0565</v>
+        <v>0.556</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0067</v>
+        <v>0.1296</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8138</v>
+        <v>1.177</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1172</v>
+        <v>-1.2173</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9309</v>
+        <v>2.3943</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7504</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0298</v>
+        <v>0.3334</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0258</v>
+        <v>-0.0743</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0556</v>
+        <v>0.4077</v>
       </c>
       <c r="V18" t="n">
         <v>1.788</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BERMEJO ALCALDE</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2744</v>
+        <v>0.8428</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1254</v>
+        <v>-0.952</v>
       </c>
       <c r="F19" t="n">
-        <v>0.149</v>
+        <v>1.7948</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7791</v>
+        <v>2.2689</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5299</v>
+        <v>1.1377</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2492</v>
+        <v>1.1311</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4812</v>
+        <v>1.621</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3388</v>
+        <v>1.4129</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8576</v>
+        <v>0.208</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2979</v>
+        <v>0.6479</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1912</v>
+        <v>-0.2752</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1067</v>
+        <v>0.9231</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.194</v>
+        <v>-2.7164</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>3.8012</v>
+        <v>0.6306</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9066</v>
+        <v>0.0838</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8946</v>
+        <v>0.5468</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5537</v>
+        <v>0.6597</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3299</v>
+        <v>1.2239</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>L. BERMEJO ALCALDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1336</v>
+        <v>-1.4836</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2523</v>
+        <v>-0.9757</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3859</v>
+        <v>-0.5079</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2689</v>
+        <v>-1.7791</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1377</v>
+        <v>-1.5299</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1311</v>
+        <v>-0.2492</v>
       </c>
       <c r="J20" t="n">
-        <v>1.621</v>
+        <v>-0.4812</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4129</v>
+        <v>-1.3388</v>
       </c>
       <c r="L20" t="n">
-        <v>0.208</v>
+        <v>0.8576</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6479</v>
+        <v>-1.2979</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2752</v>
+        <v>-0.1912</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9231</v>
+        <v>-1.1067</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7164</v>
+        <v>-0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0785</v>
+        <v>2.0432</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2165</v>
+        <v>0.8055</v>
       </c>
       <c r="U20" t="n">
-        <v>0.138</v>
+        <v>1.2377</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6597</v>
+        <v>-1.5537</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2239</v>
+        <v>-0.3299</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3132</v>
+        <v>-2.1224</v>
       </c>
       <c r="E21" t="n">
         <v>-0.4209</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8922</v>
+        <v>-1.7015</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3984</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2494</v>
+        <v>0.4402</v>
       </c>
       <c r="T21" t="n">
         <v>0.3892</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V21" t="n">
         <v>0.6119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.917</v>
+        <v>-2.8714</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1302</v>
+        <v>-2.0301</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.8413</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0448</v>
@@ -2170,13 +2170,13 @@
         <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1577</v>
+        <v>0.2033</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0247</v>
+        <v>0.1248</v>
       </c>
       <c r="U22" t="n">
-        <v>0.133</v>
+        <v>0.0785</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9941</v>
+        <v>-3.4781</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.979</v>
+        <v>-1.3784</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0151</v>
+        <v>-2.0997</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9428</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.6006</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.041</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7261</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9418</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.553</v>
+        <v>12.22040000000001</v>
       </c>
       <c r="E24" t="n">
         <v>11.5538</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0008999999999996788</v>
+        <v>0.6664000000000003</v>
       </c>
       <c r="G24" t="n">
-        <v>5.334700000000002</v>
+        <v>5.3347</v>
       </c>
       <c r="H24" t="n">
         <v>-4.1192</v>
@@ -2302,13 +2302,13 @@
         <v>12.3875</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.628000000000001</v>
+        <v>-2.628</v>
       </c>
       <c r="L24" t="n">
         <v>15.0154</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.052899999999999</v>
+        <v>-7.0529</v>
       </c>
       <c r="N24" t="n">
         <v>-1.4915</v>
@@ -2326,19 +2326,19 @@
         <v>7.761399999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>6.8529</v>
+        <v>7.5201</v>
       </c>
       <c r="T24" t="n">
         <v>2.198</v>
       </c>
       <c r="U24" t="n">
-        <v>4.6548</v>
+        <v>5.322099999999999</v>
       </c>
       <c r="V24" t="n">
         <v>3.246200000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>8.610300000000001</v>
+        <v>8.610299999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-5.3643</v>
